--- a/artfynd/S 1127-2023 artfynd.xlsx
+++ b/artfynd/S 1127-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY304"/>
+  <dimension ref="A1:AZ304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433325</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433355</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433334</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433344</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433326</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433327</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433329</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433330</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433331</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433332</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,6 +2016,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433333</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2128,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433335</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433337</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2277,6 +2352,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433338</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433341</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2491,6 +2576,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433342</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2598,6 +2688,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433347</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2705,6 +2800,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433349</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2812,6 +2912,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433351</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2919,6 +3024,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433352</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3026,6 +3136,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433354</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3133,6 +3248,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433328</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3240,6 +3360,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433336</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3347,6 +3472,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433339</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3454,6 +3584,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433340</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3561,6 +3696,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433345</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3668,6 +3808,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433350</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3775,6 +3920,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433353</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3882,6 +4032,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433343</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3989,6 +4144,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433346</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4096,6 +4256,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433300</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4203,6 +4368,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4310,6 +4480,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433111</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433167</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4524,6 +4704,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433045</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433108</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4738,6 +4928,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433205</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4845,6 +5040,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433024</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4952,6 +5152,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433027</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5059,6 +5264,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433030</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5166,6 +5376,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433103</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5273,6 +5488,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433110</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5380,6 +5600,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433112</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5487,6 +5712,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433122</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5594,6 +5824,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433125</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5701,6 +5936,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433131</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5808,6 +6048,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433132</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5915,6 +6160,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433136</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6022,6 +6272,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433137</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6129,6 +6384,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433139</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6236,6 +6496,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433141</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6343,6 +6608,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433143</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6450,6 +6720,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433145</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6557,6 +6832,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433149</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6664,6 +6944,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433154</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6771,6 +7056,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433158</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6878,6 +7168,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433159</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6985,6 +7280,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433184</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7092,6 +7392,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433299</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7199,6 +7504,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433301</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7306,6 +7616,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433304</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7413,6 +7728,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433305</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7520,6 +7840,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433306</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7627,6 +7952,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433307</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7734,6 +8064,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433311</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7841,6 +8176,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433312</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7948,6 +8288,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433313</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8055,6 +8400,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433316</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8162,6 +8512,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433317</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8269,6 +8624,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433152</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8376,6 +8736,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433187</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8483,6 +8848,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433192</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8590,6 +8960,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433314</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8697,6 +9072,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433293</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8804,6 +9184,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433295</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8911,6 +9296,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433025</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9018,6 +9408,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433028</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9125,6 +9520,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433029</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9232,6 +9632,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433046</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9339,6 +9744,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433104</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9446,6 +9856,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433106</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9553,6 +9968,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433113</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9660,6 +10080,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433115</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9767,6 +10192,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433124</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9874,6 +10304,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433127</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9981,6 +10416,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433130</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10088,6 +10528,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433133</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10195,6 +10640,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433135</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10302,6 +10752,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433138</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10409,6 +10864,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433142</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10516,6 +10976,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433144</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10623,6 +11088,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433146</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10730,6 +11200,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433148</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10837,6 +11312,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433150</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10944,6 +11424,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433153</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11051,6 +11536,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433166</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11158,6 +11648,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433168</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11265,6 +11760,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433185</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11372,6 +11872,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433188</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11479,6 +11984,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433189</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11586,6 +12096,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433190</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11693,6 +12208,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433193</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11800,6 +12320,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433195</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11907,6 +12432,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433196</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12014,6 +12544,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433198</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12121,6 +12656,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433202</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12228,6 +12768,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433204</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12335,6 +12880,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433207</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12442,6 +12992,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433302</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12549,6 +13104,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433303</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12656,6 +13216,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433315</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12763,6 +13328,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433298</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12870,6 +13440,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433147</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12985,6 +13560,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433318</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13092,6 +13672,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433324</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13199,6 +13784,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433107</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13306,6 +13896,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433114</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13413,6 +14008,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433117</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13520,6 +14120,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433123</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13627,6 +14232,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433129</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13734,6 +14344,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433140</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13841,6 +14456,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433157</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13948,6 +14568,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433186</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14055,6 +14680,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433191</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14162,6 +14792,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433197</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14269,6 +14904,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433200</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14376,6 +15016,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433208</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14483,6 +15128,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433290</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14590,6 +15240,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433102</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14697,6 +15352,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433105</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14804,6 +15464,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433109</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14911,6 +15576,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433128</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15018,6 +15688,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433134</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15125,6 +15800,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433194</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15232,6 +15912,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433199</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15339,6 +16024,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433201</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15446,6 +16136,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433203</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15553,6 +16248,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433206</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15660,6 +16360,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433289</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15767,6 +16472,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433291</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15874,6 +16584,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433294</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15981,6 +16696,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433297</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16088,6 +16808,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433308</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16195,6 +16920,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433057</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16302,6 +17032,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433061</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16409,6 +17144,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433032</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16516,6 +17256,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433048</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16623,6 +17368,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433055</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16730,6 +17480,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433085</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16837,6 +17592,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433036</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16944,6 +17704,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433100</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17051,6 +17816,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433067</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17158,6 +17928,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433031</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17265,6 +18040,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433033</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17372,6 +18152,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433034</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17479,6 +18264,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433037</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17586,6 +18376,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433038</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17693,6 +18488,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433039</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17800,6 +18600,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433040</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17907,6 +18712,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433042</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18014,6 +18824,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433049</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18121,6 +18936,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433051</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18228,6 +19048,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433059</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18335,6 +19160,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433062</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18442,6 +19272,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433064</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18549,6 +19384,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433065</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18656,6 +19496,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433068</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18763,6 +19608,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433070</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18870,6 +19720,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433071</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18977,6 +19832,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433074</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19084,6 +19944,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433075</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19191,6 +20056,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433076</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19298,6 +20168,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433077</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19405,6 +20280,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433083</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19512,6 +20392,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433084</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19619,6 +20504,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433086</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19726,6 +20616,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433088</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19833,6 +20728,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433093</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19940,6 +20840,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433094</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20047,6 +20952,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433095</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20154,6 +21064,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433096</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20261,6 +21176,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433097</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20368,6 +21288,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433098</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20475,6 +21400,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433101</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20582,6 +21512,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433090</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20689,6 +21624,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433035</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20796,6 +21736,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433041</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20903,6 +21848,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433044</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21010,6 +21960,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433052</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21117,6 +22072,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433054</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21224,6 +22184,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433058</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21331,6 +22296,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433069</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21438,6 +22408,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433072</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21545,6 +22520,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433073</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21652,6 +22632,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433078</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21759,6 +22744,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433079</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21866,6 +22856,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433081</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21973,6 +22968,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433082</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22080,6 +23080,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433089</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22187,6 +23192,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433091</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22294,6 +23304,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433092</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22401,6 +23416,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433287</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22508,6 +23528,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433087</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22615,6 +23640,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433099</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22722,6 +23752,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433080</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22829,6 +23864,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433252</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22936,6 +23976,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433279</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23043,6 +24088,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433240</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23150,6 +24200,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433253</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23257,6 +24312,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433255</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23364,6 +24424,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433256</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23471,6 +24536,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433262</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23578,6 +24648,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433265</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23685,6 +24760,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433272</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23792,6 +24872,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433273</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23899,6 +24984,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433276</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24006,6 +25096,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433259</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24113,6 +25208,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433264</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24220,6 +25320,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433251</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24327,6 +25432,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433258</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24434,6 +25544,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433260</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24541,6 +25656,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433261</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24648,6 +25768,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433263</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24755,6 +25880,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433266</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24862,6 +25992,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433274</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24969,6 +26104,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433275</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25076,6 +26216,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433277</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25183,6 +26328,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433239</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25290,6 +26440,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433257</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25397,6 +26552,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433267</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25504,6 +26664,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433278</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25611,6 +26776,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433254</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25718,6 +26888,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433271</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25825,6 +27000,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433178</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25932,6 +27112,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433170</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -26039,6 +27224,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433250</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -26146,6 +27336,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433281</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26253,6 +27448,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433121</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26360,6 +27560,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433177</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26467,6 +27672,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433222</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26574,6 +27784,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433246</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26681,6 +27896,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433247</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26788,6 +28008,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433161</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26895,6 +28120,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433164</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -27002,6 +28232,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433169</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -27109,6 +28344,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433172</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -27216,6 +28456,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433174</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27323,6 +28568,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433175</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27430,6 +28680,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433179</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27537,6 +28792,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433181</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27644,6 +28904,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433182</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27751,6 +29016,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433209</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27858,6 +29128,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433212</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27965,6 +29240,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433216</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -28072,6 +29352,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433217</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -28179,6 +29464,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433218</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -28286,6 +29576,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433221</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -28393,6 +29688,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433234</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -28500,6 +29800,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433238</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -28607,6 +29912,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433162</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -28714,6 +30024,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433233</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28821,6 +30136,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433225</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28928,6 +30248,11 @@
         </is>
       </c>
       <c r="AY265" t="inlineStr"/>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433213</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -29035,6 +30360,11 @@
         </is>
       </c>
       <c r="AY266" t="inlineStr"/>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433119</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -29142,6 +30472,11 @@
         </is>
       </c>
       <c r="AY267" t="inlineStr"/>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433155</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -29249,6 +30584,11 @@
         </is>
       </c>
       <c r="AY268" t="inlineStr"/>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433156</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -29356,6 +30696,11 @@
         </is>
       </c>
       <c r="AY269" t="inlineStr"/>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433160</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -29463,6 +30808,11 @@
         </is>
       </c>
       <c r="AY270" t="inlineStr"/>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433163</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -29570,6 +30920,11 @@
         </is>
       </c>
       <c r="AY271" t="inlineStr"/>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433165</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -29677,6 +31032,11 @@
         </is>
       </c>
       <c r="AY272" t="inlineStr"/>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433171</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -29784,6 +31144,11 @@
         </is>
       </c>
       <c r="AY273" t="inlineStr"/>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433173</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -29891,6 +31256,11 @@
         </is>
       </c>
       <c r="AY274" t="inlineStr"/>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433176</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -29998,6 +31368,11 @@
         </is>
       </c>
       <c r="AY275" t="inlineStr"/>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433211</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -30105,6 +31480,11 @@
         </is>
       </c>
       <c r="AY276" t="inlineStr"/>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433220</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -30212,6 +31592,11 @@
         </is>
       </c>
       <c r="AY277" t="inlineStr"/>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433226</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -30319,6 +31704,11 @@
         </is>
       </c>
       <c r="AY278" t="inlineStr"/>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433228</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -30426,6 +31816,11 @@
         </is>
       </c>
       <c r="AY279" t="inlineStr"/>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433232</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -30533,6 +31928,11 @@
         </is>
       </c>
       <c r="AY280" t="inlineStr"/>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433235</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -30640,6 +32040,11 @@
         </is>
       </c>
       <c r="AY281" t="inlineStr"/>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433236</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -30747,6 +32152,11 @@
         </is>
       </c>
       <c r="AY282" t="inlineStr"/>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433237</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -30854,6 +32264,11 @@
         </is>
       </c>
       <c r="AY283" t="inlineStr"/>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433241</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -30961,6 +32376,11 @@
         </is>
       </c>
       <c r="AY284" t="inlineStr"/>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433243</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -31068,6 +32488,11 @@
         </is>
       </c>
       <c r="AY285" t="inlineStr"/>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433280</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -31175,6 +32600,11 @@
         </is>
       </c>
       <c r="AY286" t="inlineStr"/>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433284</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -31282,6 +32712,11 @@
         </is>
       </c>
       <c r="AY287" t="inlineStr"/>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433286</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -31389,6 +32824,11 @@
         </is>
       </c>
       <c r="AY288" t="inlineStr"/>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433180</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -31496,6 +32936,11 @@
         </is>
       </c>
       <c r="AY289" t="inlineStr"/>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433118</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -31603,6 +33048,11 @@
         </is>
       </c>
       <c r="AY290" t="inlineStr"/>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433120</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -31710,6 +33160,11 @@
         </is>
       </c>
       <c r="AY291" t="inlineStr"/>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433183</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -31817,6 +33272,11 @@
         </is>
       </c>
       <c r="AY292" t="inlineStr"/>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433219</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -31924,6 +33384,11 @@
         </is>
       </c>
       <c r="AY293" t="inlineStr"/>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433223</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -32031,6 +33496,11 @@
         </is>
       </c>
       <c r="AY294" t="inlineStr"/>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433224</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -32138,6 +33608,11 @@
         </is>
       </c>
       <c r="AY295" t="inlineStr"/>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433227</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -32245,6 +33720,11 @@
         </is>
       </c>
       <c r="AY296" t="inlineStr"/>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433229</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -32352,6 +33832,11 @@
         </is>
       </c>
       <c r="AY297" t="inlineStr"/>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433230</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -32459,6 +33944,11 @@
         </is>
       </c>
       <c r="AY298" t="inlineStr"/>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433231</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -32566,6 +34056,11 @@
         </is>
       </c>
       <c r="AY299" t="inlineStr"/>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433242</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -32673,6 +34168,11 @@
         </is>
       </c>
       <c r="AY300" t="inlineStr"/>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433244</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -32780,6 +34280,11 @@
         </is>
       </c>
       <c r="AY301" t="inlineStr"/>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433248</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -32887,6 +34392,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433282</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -32994,6 +34504,11 @@
         </is>
       </c>
       <c r="AY303" t="inlineStr"/>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433283</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -33101,8 +34616,318 @@
         </is>
       </c>
       <c r="AY304" t="inlineStr"/>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134433285</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>